--- a/southern_europe/italy_data/network_capex_metrics/gamma_defined_per_arc_pipeline.xlsx
+++ b/southern_europe/italy_data/network_capex_metrics/gamma_defined_per_arc_pipeline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gamma1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="gamma2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="gamma3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="gamma4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gamma1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gamma2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gamma3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gamma4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>20725826.022</v>
+        <v>42415003.756</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>43057180.63</v>
+        <v>81276152.46799999</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -862,13 +862,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>11111337.052</v>
+        <v>23857676.3</v>
       </c>
       <c r="I4" t="n">
-        <v>9374947.4</v>
+        <v>20230040.131</v>
       </c>
       <c r="J4" t="n">
-        <v>11259128.566</v>
+        <v>24566107.257</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4801455.485</v>
+        <v>14218044.938</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1011,10 +1011,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>14472504.464</v>
+        <v>31333602.205</v>
       </c>
       <c r="M5" t="n">
-        <v>17632236.782</v>
+        <v>37172018.482</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9529119.721000001</v>
+        <v>21740369.21</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1148,10 +1148,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11642916.786</v>
+        <v>27189578.781</v>
       </c>
       <c r="M6" t="n">
-        <v>14447067.671</v>
+        <v>31701988.748</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4941762.442</v>
+        <v>12974409.435</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>11297084.464</v>
+        <v>23869017.067</v>
       </c>
       <c r="N7" t="n">
-        <v>6930708.091</v>
+        <v>17793207.158</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1407,13 +1407,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3949812.122</v>
+        <v>11730239.758</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4848259.473</v>
+        <v>14628727.677</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1428,16 +1428,16 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>7574350.7</v>
+        <v>20782775.394</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11577246.415</v>
+        <v>26222534.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>12252775.946</v>
+        <v>29830070.365</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1547,13 +1547,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4206781.643</v>
+        <v>12744966.328</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5965737.115</v>
+        <v>16070737.594</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8885480.777000001</v>
+        <v>21278939.735</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>10923692.194</v>
+        <v>24473117.611</v>
       </c>
       <c r="Q9" t="n">
-        <v>11287538.739</v>
+        <v>25748136.107</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5341911.006</v>
+        <v>15659104.044</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>19315754.459</v>
+        <v>44217984.188</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1708,10 +1708,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>11234613.437</v>
+        <v>28381164.148</v>
       </c>
       <c r="Q10" t="n">
-        <v>9284653.771</v>
+        <v>23988990.942</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>17246111.729</v>
+        <v>40501765.454</v>
       </c>
       <c r="V10" t="n">
-        <v>26220602.194</v>
+        <v>54958613.169</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11567162.042</v>
+        <v>26454038.715</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>27046672.051</v>
+        <v>50722193.391</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>9775222.384</v>
+        <v>23470216.614</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1988,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>10472449.158</v>
+        <v>23085448.641</v>
       </c>
       <c r="S12" t="n">
-        <v>13960677.761</v>
+        <v>27151291.106</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>6534473.007</v>
+        <v>15784427.902</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6484911.455</v>
+        <v>17189734.179</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>11090227.769</v>
+        <v>24960323.752</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5427848.161</v>
+        <v>16936531.862</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2253,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>7790816.599</v>
+        <v>21627906.03</v>
       </c>
       <c r="P14" t="n">
-        <v>8975228.963</v>
+        <v>24384935.009</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2387,13 +2387,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3771438.312</v>
+        <v>10966608.059</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8894438.436000001</v>
+        <v>21771987.533</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>13124905.624</v>
+        <v>28443880.994</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>20982900.717</v>
+        <v>41801334.642</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6288574.633</v>
+        <v>16079398.035</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>12344581.731</v>
+        <v>25297804.314</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>18159647.818</v>
+        <v>36229621.513</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>8495935.429</v>
+        <v>19227268.788</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>8801282.557</v>
+        <v>21220721.149</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2932,13 +2932,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5227002.481</v>
+        <v>16651106.01</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10913107.797</v>
+        <v>28243241.037</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>6651378.626</v>
+        <v>18683751.916</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>7070702.592</v>
+        <v>17713568.353</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3473528.167</v>
+        <v>10192077.756</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>15571488.382</v>
+        <v>33305146.67</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>15310138.6</v>
+        <v>30290841.445</v>
       </c>
       <c r="X20" t="n">
-        <v>14588274.417</v>
+        <v>30509737.959</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -3239,16 +3239,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>14951711.211</v>
+        <v>35425920.34</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>12777354.246</v>
+        <v>30579770.908</v>
       </c>
       <c r="AA21" t="n">
-        <v>25659160.493</v>
+        <v>57037024.255</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>16606349.112</v>
+        <v>38834598.098</v>
       </c>
     </row>
     <row r="22">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>7530702.863</v>
+        <v>21235278.127</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>14500828.738</v>
+        <v>31187130.514</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3501,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>7974339.159</v>
+        <v>18070278.903</v>
       </c>
       <c r="U23" t="n">
-        <v>19747328.541</v>
+        <v>39131526.526</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>10922632.506</v>
+        <v>22851984.854</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>12541828.081</v>
+        <v>31457077.867</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>5346379.34</v>
+        <v>16007361.023</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3787,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3019274.436</v>
+        <v>9963152.275</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>17371958.526</v>
+        <v>40442621.586</v>
       </c>
       <c r="AA25" t="n">
-        <v>16862932.58</v>
+        <v>37435978.757</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>17010654.819</v>
+        <v>38569332.94</v>
       </c>
     </row>
     <row r="26">
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>14419978.42</v>
+        <v>31533840.327</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3936,13 +3936,13 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>11887336.562</v>
+        <v>26394919.855</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>20135237.566</v>
+        <v>42314653.738</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>6286914.042</v>
+        <v>17341318.164</v>
       </c>
     </row>
     <row r="27">
@@ -4073,28 +4073,28 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>18226518.646</v>
+        <v>37853238.431</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>16195261.047</v>
+        <v>34407444.573</v>
       </c>
       <c r="AE27" t="n">
-        <v>23013899.923</v>
+        <v>47267818.899</v>
       </c>
       <c r="AF27" t="n">
-        <v>14736605.761</v>
+        <v>31211039.233</v>
       </c>
       <c r="AG27" t="n">
-        <v>14468978.655</v>
+        <v>31083590.453</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>17571312.2</v>
+        <v>36152091.587</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>13900223.769</v>
+        <v>30262259.733</v>
       </c>
     </row>
     <row r="28">
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>15922645.239</v>
+        <v>33929742.998</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4216,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>11723950.81</v>
+        <v>26060428.985</v>
       </c>
       <c r="AE28" t="n">
-        <v>12095805.123</v>
+        <v>25462334.791</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>42863877.014</v>
+        <v>74611728.858</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4365,10 +4365,10 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>30631832.97</v>
+        <v>53831949.516</v>
       </c>
       <c r="AI29" t="n">
-        <v>41321354.793</v>
+        <v>73148418.499</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -4493,13 +4493,13 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>9645032.526000001</v>
+        <v>21284412.087</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>5653504.381</v>
+        <v>15111026.766</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
@@ -4508,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17656215.019</v>
+        <v>37324103.938</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>15413974.664</v>
+        <v>33043120.993</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>8414252.550000001</v>
+        <v>19153696.525</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15002116.384</v>
+        <v>31751557.854</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>13850255.241</v>
+        <v>30172036.445</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>6035405.064</v>
+        <v>17059324.003</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>7815207.91</v>
+        <v>20057588.837</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>21383688.006</v>
+        <v>48562664.182</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>5218473.715</v>
+        <v>13940183.318</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>5223805.445</v>
+        <v>13956063.272</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>17221705.652</v>
+        <v>35289386.884</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
@@ -5053,19 +5053,19 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>14840099.291</v>
+        <v>32745698.132</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>9077992.708000001</v>
+        <v>20356184.891</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>16428666.588</v>
+        <v>35942124.532</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>5364717.35</v>
+        <v>14311405.679</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -5202,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>10265354.688</v>
+        <v>23220207.128</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>5628128.291</v>
+        <v>14910239.647</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
@@ -5345,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>16696109.511</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
         <v>0</v>
@@ -5461,10 +5461,10 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>6209624.441</v>
+        <v>14786172.722</v>
       </c>
       <c r="AI37" t="n">
-        <v>13689891.675</v>
+        <v>29048097.177</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>12719385.223</v>
+        <v>26656339.891</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>5186532.415</v>
+        <v>15471903.293</v>
       </c>
       <c r="AR38" t="n">
         <v>0</v>
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>6597327.838</v>
+        <v>16082792.229</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
@@ -5881,13 +5881,13 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>17544317.781</v>
+        <v>38168577.422</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>21273343.257</v>
+        <v>46330025.603</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>15185780.988</v>
+        <v>31392054.327</v>
       </c>
       <c r="AM41" t="n">
         <v>0</v>
@@ -6155,13 +6155,13 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>26070312.183</v>
+        <v>52667250.055</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>23700399.371</v>
+        <v>48637206.882</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>3042015.556</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
@@ -6533,19 +6533,19 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>5441450.231</v>
+        <v>14462315.458</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>9687115.025</v>
+        <v>20905444.884</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>15950315.116</v>
+        <v>33107662.378</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>396836.255</v>
+        <v>91758.05</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>676760.808</v>
+        <v>128734.902</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>223685.926</v>
+        <v>81427.056</v>
       </c>
       <c r="I4" t="n">
-        <v>200033.479</v>
+        <v>78626.535</v>
       </c>
       <c r="J4" t="n">
-        <v>242224.784</v>
+        <v>82199.867</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>176842.288</v>
+        <v>60225.772</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7187,10 +7187,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>304159.013</v>
+        <v>77162.056</v>
       </c>
       <c r="M5" t="n">
-        <v>341784.483</v>
+        <v>87139.57399999999</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>215126.677</v>
+        <v>70674.158</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -7324,10 +7324,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>251775.852</v>
+        <v>70715.98</v>
       </c>
       <c r="M6" t="n">
-        <v>284064.136</v>
+        <v>79650.39</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>170867.185</v>
+        <v>62966.587</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7464,10 +7464,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>249986.237</v>
+        <v>73849.318</v>
       </c>
       <c r="N7" t="n">
-        <v>231461.651</v>
+        <v>67539.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7583,13 +7583,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>139835.638</v>
+        <v>58254.037</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>174787.935</v>
+        <v>63505.834</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7604,16 +7604,16 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>217472.309</v>
+        <v>67932.69</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>239420.551</v>
+        <v>78019.83900000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>256304.465</v>
+        <v>83916.85000000001</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -7723,13 +7723,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>153257.355</v>
+        <v>58404.298</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>167892.99</v>
+        <v>64751.862</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>205091.481</v>
+        <v>72716.429</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>227076.685</v>
+        <v>77442.891</v>
       </c>
       <c r="Q9" t="n">
-        <v>232682.486</v>
+        <v>79688.268</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>151975.818</v>
+        <v>60813.532</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>379760.435</v>
+        <v>86719.368</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -7884,10 +7884,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>233404.831</v>
+        <v>78253.76300000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>212235.556</v>
+        <v>74606.541</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -7899,10 +7899,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>319952.724</v>
+        <v>92061.249</v>
       </c>
       <c r="V10" t="n">
-        <v>444151.591</v>
+        <v>102136.535</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>242960.938</v>
+        <v>83922.226</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8039,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>497371.661</v>
+        <v>102882.883</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -8149,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>332512.107</v>
+        <v>72593.427</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -8164,10 +8164,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>288184.843</v>
+        <v>71743.459</v>
       </c>
       <c r="S12" t="n">
-        <v>305926.415</v>
+        <v>79166.639</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>154168.234</v>
+        <v>64268.775</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>266135.957</v>
+        <v>68595.49800000001</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>319638.71</v>
+        <v>74325.145</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>161661.065</v>
+        <v>60064.483</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -8429,10 +8429,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>270786.575</v>
+        <v>67483.019</v>
       </c>
       <c r="P14" t="n">
-        <v>254905.38</v>
+        <v>67419.90700000001</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8563,13 +8563,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>141530.392</v>
+        <v>57492.597</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>278679.533</v>
+        <v>70370.77499999999</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8581,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>275039.345</v>
+        <v>75257.49000000001</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8593,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>381365.795</v>
+        <v>102488.15</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -8709,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>186910.71</v>
+        <v>67194.817</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>251513.631</v>
+        <v>86278.55100000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>351062.91</v>
+        <v>101548.105</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>181067.282</v>
+        <v>70713.618</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -8989,7 +8989,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>286108.794</v>
+        <v>69998.38400000001</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -9108,13 +9108,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>163654.392</v>
+        <v>59753.364</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>294160.571</v>
+        <v>70365.421</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>236369.709</v>
+        <v>64001.165</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -9251,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>159526.24</v>
+        <v>65328.729</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9263,22 +9263,22 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>132736.25</v>
+        <v>56219.297</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>323337.953</v>
+        <v>94690.977</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>299034.074</v>
+        <v>80204.81299999999</v>
       </c>
       <c r="X20" t="n">
-        <v>302925.872</v>
+        <v>84462.874</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -9415,16 +9415,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>300346.43</v>
+        <v>90748.696</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>275595.844</v>
+        <v>85897.75999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>435008.9</v>
+        <v>119879.681</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>310322.394</v>
+        <v>96412.89599999999</v>
       </c>
     </row>
     <row r="22">
@@ -9543,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>248070.676</v>
+        <v>66242.489</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -9558,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>273099.537</v>
+        <v>78767.959</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -9677,10 +9677,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>168587.082</v>
+        <v>70106.698</v>
       </c>
       <c r="U23" t="n">
-        <v>347201.175</v>
+        <v>104167.179</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>266646.859</v>
+        <v>74065.05899999999</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -9817,7 +9817,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>256733.485</v>
+        <v>85560.58</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>225775.014</v>
+        <v>64494.82</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -9963,16 +9963,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>135586.899</v>
+        <v>55912.657</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>324566.089</v>
+        <v>97120.34600000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>342708.225</v>
+        <v>88347.264</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>315423.399</v>
+        <v>93688.014</v>
       </c>
     </row>
     <row r="26">
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>275936.202</v>
+        <v>93401.05</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -10112,13 +10112,13 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>248859.702</v>
+        <v>82533.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>364919.482</v>
+        <v>112553.684</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
         <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>193229.253</v>
+        <v>66333.999</v>
       </c>
     </row>
     <row r="27">
@@ -10249,28 +10249,28 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>325434.931</v>
+        <v>104050.32</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>318693.35</v>
+        <v>98346.515</v>
       </c>
       <c r="AE27" t="n">
-        <v>411300.821</v>
+        <v>118451.711</v>
       </c>
       <c r="AF27" t="n">
-        <v>300326.36</v>
+        <v>90541.42999999999</v>
       </c>
       <c r="AG27" t="n">
-        <v>284856.764</v>
+        <v>93163.788</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>342066.528</v>
+        <v>97535.11</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -10300,7 +10300,7 @@
         <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>291864.947</v>
+        <v>90522.912</v>
       </c>
     </row>
     <row r="28">
@@ -10383,7 +10383,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>288320.936</v>
+        <v>97998.43799999999</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -10392,10 +10392,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>246328.323</v>
+        <v>86138.408</v>
       </c>
       <c r="AE28" t="n">
-        <v>234014.031</v>
+        <v>79810.41899999999</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -10520,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>691020.8100000001</v>
+        <v>135112.988</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -10541,10 +10541,10 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>494395.23</v>
+        <v>110023.916</v>
       </c>
       <c r="AI29" t="n">
-        <v>664412.25</v>
+        <v>138130.54</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -10669,13 +10669,13 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>211175.566</v>
+        <v>78469.757</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>174063.459</v>
+        <v>65433.618</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
@@ -10684,13 +10684,13 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>330174.219</v>
+        <v>105542.607</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>305286.359</v>
+        <v>98410.531</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>186278.964</v>
+        <v>73503.757</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -10821,13 +10821,13 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>293208.677</v>
+        <v>92801.117</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>280969.489</v>
+        <v>91546.08199999999</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
@@ -10949,13 +10949,13 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>186156.717</v>
+        <v>64671.107</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>212238.573</v>
+        <v>67006.74800000001</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -10964,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>386527.229</v>
+        <v>113609.848</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -11077,13 +11077,13 @@
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>161153.811</v>
+        <v>62126.383</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>163611.695</v>
+        <v>62200.099</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>309869.527</v>
+        <v>104407.672</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
@@ -11229,19 +11229,19 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>299817.779</v>
+        <v>86679.27899999999</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>205147.596</v>
+        <v>69937.83900000001</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>332903.751</v>
+        <v>89524.818</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -11357,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>152231.264</v>
+        <v>61563.036</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -11378,7 +11378,7 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>240014.866</v>
+        <v>72409.234</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>168505.557</v>
+        <v>64864.063</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
@@ -11521,7 +11521,7 @@
         <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>343878.465</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
         <v>0</v>
@@ -11637,10 +11637,10 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>147428.998</v>
+        <v>64346.834</v>
       </c>
       <c r="AI37" t="n">
-        <v>279344.437</v>
+        <v>87847.246</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -11652,7 +11652,7 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>259417.902</v>
+        <v>80013.78200000001</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -11801,7 +11801,7 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>170390.846</v>
+        <v>62376.046</v>
       </c>
       <c r="AR38" t="n">
         <v>0</v>
@@ -11914,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>162309.229</v>
+        <v>65037.762</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
@@ -12057,13 +12057,13 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>359509.47</v>
+        <v>87811.016</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>370480.205</v>
+        <v>106670.465</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -12197,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>308187.102</v>
+        <v>91293.594</v>
       </c>
       <c r="AM41" t="n">
         <v>0</v>
@@ -12331,13 +12331,13 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>438126.995</v>
+        <v>127081.526</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>402027.944</v>
+        <v>121735.992</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -12489,7 +12489,7 @@
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>213074.604</v>
+        <v>13273.625</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
@@ -12709,19 +12709,19 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>169474.854</v>
+        <v>63025.866</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>211820.732</v>
+        <v>78983.13099999999</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>300453.543</v>
+        <v>100160.418</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
